--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260527_214607.xlsx
@@ -5904,7 +5904,7 @@
       </c>
       <c r="P76" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6052,7 +6052,7 @@
       </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6286,7 +6286,7 @@
       </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -6352,7 +6352,7 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="P83" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6970,7 +6970,7 @@
       </c>
       <c r="P91" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8208,7 +8208,7 @@
       </c>
       <c r="P109" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8284,7 +8284,7 @@
       </c>
       <c r="P110" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -8360,7 +8360,7 @@
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
